--- a/survey_templates/049_grocery_store_survey--survey_templates.xlsx
+++ b/survey_templates/049_grocery_store_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,398 +554,375 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>date_visited</t>
+          <t>overall_rating</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Date Visited</t>
+          <t>Overall Rating</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>time_spent</t>
+          <t>product_and_price_rating</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Time Spent</t>
+          <t>Product and Price Rating</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>employee_name</t>
+          <t>store_appearance_and_cleanliness</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Employee Name</t>
+          <t>Store Appearance and Cleanliness</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>employee_name_2</t>
+          <t>store_layout</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Employee Name 2</t>
+          <t>Store Layout</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>overall_rating</t>
+          <t>employee_attitude</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Overall Rating</t>
+          <t>Employee Attitude</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question1</t>
+          <t>time_spent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How would you rate your experience at this store?</t>
+          <t>Time Spent</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question1_2</t>
+          <t>date_visited</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How would you rate your experience at this store?</t>
+          <t>Date Visited</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question2</t>
+          <t>employee_name</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How would you rate the store's products and prices?</t>
+          <t>Employee Name</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question2_2</t>
+          <t>employee_name_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How would you rate the store's products and prices?</t>
+          <t>Employee Name 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question3</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How would you rate the store's service?</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question3_2</t>
+          <t>question1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How would you rate the store's service?</t>
+          <t>How would you rate the store's products and prices?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question4</t>
+          <t>question1_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How would you rate the store's store appearance and cleanliness?</t>
+          <t>Question1 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question4_2</t>
+          <t>question2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How would you rate the store's store appearance and cleanliness?</t>
+          <t>How would you rate the store's service?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>question5</t>
+          <t>question2_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>How would you rate the store's store layout?</t>
+          <t>Question2 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>question5_2</t>
+          <t>question3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>How would you rate the store's store layout?</t>
+          <t>How would you rate the store's store appearance and cleanliness?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>question6</t>
+          <t>question3_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>How would you rate the store's employees' attitude?</t>
+          <t>Question3 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question6_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>How would you rate the store's employees' attitude?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -960,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -988,238 +965,238 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question1_choices</t>
+          <t>overall_rating_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1_-_1</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1 - 1</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question1_choices</t>
+          <t>overall_rating_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2_-_2</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2 - 2</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question1_choices</t>
+          <t>product_and_price_rating_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3_-_3</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3 - 3</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question1_choices</t>
+          <t>product_and_price_rating_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4_-_4</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4 - 4</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question1_choices</t>
+          <t>store_appearance_and_cleanliness_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5_-_5</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5 - 5</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question1_2_choices</t>
+          <t>store_appearance_and_cleanliness_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1_-_1</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1 - 1</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question1_2_choices</t>
+          <t>store_layout_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2_-_2</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2 - 2</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question1_2_choices</t>
+          <t>store_layout_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3_-_3</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3 - 3</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question1_2_choices</t>
+          <t>employee_attitude_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4_-_4</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4 - 4</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question1_2_choices</t>
+          <t>employee_attitude_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5_-_5</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5 - 5</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question2_choices</t>
+          <t>question1_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1_-_1</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1 - 1</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question2_choices</t>
+          <t>question1_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2_-_2</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2 - 2</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question2_choices</t>
+          <t>question1_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3_-_3</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3 - 3</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question2_choices</t>
+          <t>question1_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4_-_4</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4 - 4</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
@@ -1231,29 +1208,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5_-_5</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5 - 5</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question2_2_choices</t>
+          <t>question2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1_-_1</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1 - 1</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1242,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2_-_2</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2 - 2</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
@@ -1282,726 +1259,80 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3_-_3</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3 - 3</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question2_2_choices</t>
+          <t>question3_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4_-_4</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4 - 4</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question2_2_choices</t>
+          <t>question3_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5_-_5</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5 - 5</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question3_choices</t>
+          <t>question3_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1_-_1</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1 - 1</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>question3_choices</t>
+          <t>question3_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2_-_2</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2 - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>question3_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3_-_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>3 - 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>question3_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>4_-_4</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>4 - 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>question3_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>5_-_5</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>5 - 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>question3_2_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1_-_1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1 - 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>question3_2_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2_-_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2 - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>question3_2_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3_-_3</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>3 - 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>question3_2_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>4_-_4</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>4 - 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>question3_2_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>5_-_5</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>5 - 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>question4_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1_-_1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1 - 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>question4_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2_-_2</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2 - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>question4_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3_-_3</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>3 - 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>question4_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4_-_4</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>4 - 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>question4_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>5_-_5</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>5 - 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>question4_2_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>1_-_1</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1 - 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>question4_2_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2_-_2</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2 - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>question4_2_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>3_-_3</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>3 - 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>question4_2_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>4_-_4</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>4 - 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>question4_2_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>5_-_5</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>5 - 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>question5_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>1_-_1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1 - 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>question5_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2_-_2</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2 - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>question5_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>3_-_3</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>3 - 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>question5_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>4_-_4</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>4 - 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>question5_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>5_-_5</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>5 - 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>question5_2_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>1_-_1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1 - 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>question5_2_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2_-_2</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2 - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>question5_2_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>3_-_3</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>3 - 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>question5_2_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>4_-_4</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>4 - 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>question5_2_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>5_-_5</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>5 - 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>question6_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>1_-_1</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1 - 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>question6_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2_-_2</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2 - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>question6_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>3_-_3</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>3 - 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>question6_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>4_-_4</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>4 - 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>question6_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>5_-_5</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>5 - 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>question6_2_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>1_-_1</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1 - 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>question6_2_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2_-_2</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2 - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>question6_2_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>3_-_3</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>3 - 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>question6_2_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>4_-_4</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>4 - 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>question6_2_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>5_-_5</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>5 - 5</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
